--- a/checklist_forms/044_daily_vehicle_inspection_report--checklist_forms.xlsx
+++ b/checklist_forms/044_daily_vehicle_inspection_report--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>oil_low</t>
+          <t>oil low</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>oil_medium</t>
+          <t>oil medium</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>steering_well</t>
+          <t>steering well</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>not_steering</t>
+          <t>not steering</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>working_fine</t>
+          <t>working fine</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>not_working</t>
+          <t>not working</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>not applicable</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>not applicable</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>not applicable</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>under_inflated</t>
+          <t>under inflated</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>not_specified</t>
+          <t>not specified</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>not applicable</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>not_good</t>
+          <t>not good</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>not_specified</t>
+          <t>not specified</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>not_working</t>
+          <t>not working</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>not applicable</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>not applicable</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>not_specified</t>
+          <t>not specified</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>not_specified</t>
+          <t>not specified</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>not_specified</t>
+          <t>not specified</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>not applicable</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>not applicable</t>
         </is>
       </c>
     </row>
